--- a/results/log_pv_cap/log_pv_cap_densities_fdensity_effects.xlsx
+++ b/results/log_pv_cap/log_pv_cap_densities_fdensity_effects.xlsx
@@ -511,388 +511,388 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fdensity</t>
+          <t>D(Firms)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-0.191</t>
+          <t>-0.114</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.012</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-0.126</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.020</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.008</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>-0.199</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.030</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.024</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-0.005</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>0.005</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-0.010</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.025</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6.936</t>
+          <t>7.778</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.580</t>
+          <t>-0.141</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.516</t>
+          <t>7.919</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.366</t>
+          <t>5.207</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>0.320</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.486</t>
+          <t>4.887</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.371</t>
+          <t>5.042</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.509</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.318</t>
+          <t>4.533</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-2.228</t>
+          <t>1.698</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.418</t>
+          <t>1.027</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-1.810</t>
+          <t>0.670</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.143</t>
+          <t>4.114</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2.056</t>
+          <t>3.785</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.088</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3.468</t>
+          <t>4.295</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2.823</t>
+          <t>4.164</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>0.131</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.861</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.219</t>
+          <t>-0.330</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>0.793</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.046</t>
+          <t>-0.066</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.827</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.032</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>1.411</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.270</t>
+          <t>0.854</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1.170</t>
+          <t>0.557</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.887</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.027</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.389</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.014</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.367</t>
+          <t>-0.375</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.131</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.099</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.032</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.230</t>
+          <t>-0.248</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>-0.035</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-0.214</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-0.105</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-0.064</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-0.041</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-0.124</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-0.114</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>-0.010</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>-0.119</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>-0.116</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>-0.004</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-0.226</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-0.037</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-0.007</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-0.030</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.112</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.073</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.039</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>-0.096</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-0.078</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-0.018</t>
         </is>
       </c>
     </row>
